--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c.1487</t>
+          <t>environ 1487</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>c.1546</t>
+          <t>environ 1546</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>c.1520</t>
+          <t>environ 1520</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>c.1488</t>
+          <t>environ 1488</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>c.1470</t>
+          <t>environ 1470</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>c.1507</t>
+          <t>environ 1507</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>c.1568</t>
+          <t>environ 1568</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>c.1523</t>
+          <t>environ 1523</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>c.1509</t>
+          <t>environ 1509</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>c.1563</t>
+          <t>environ 1563</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>c.1430</t>
+          <t>environ 1430</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>c.1513</t>
+          <t>environ 1513</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>c.1529</t>
+          <t>environ 1529</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>c.1485</t>
+          <t>environ 1485</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>c.1507</t>
+          <t>environ 1507</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>c.1560</t>
+          <t>environ 1560</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>c.1495</t>
+          <t>environ 1495</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>c.1500</t>
+          <t>environ 1500</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>c.1470</t>
+          <t>environ 1470</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>c.1526</t>
+          <t>environ 1526</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>c.1500</t>
+          <t>environ 1500</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>c.1485</t>
+          <t>environ 1485</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>c.1540</t>
+          <t>environ 1540</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>c.1510</t>
+          <t>environ 1510</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>c.1565</t>
+          <t>environ 1565</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>c.1484</t>
+          <t>environ 1484</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>c.1540</t>
+          <t>environ 1540</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>c.1580</t>
+          <t>environ 1580</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>c.1560-1570</t>
+          <t>environ 1560-1570</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>c.1515</t>
+          <t>environ 1515</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>c.1550</t>
+          <t>environ 1550</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>c.1470</t>
+          <t>environ 1470</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>c.1530</t>
+          <t>environ 1530</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>c.1533</t>
+          <t>environ 1533</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>c.1465</t>
+          <t>environ 1465</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>c.1522</t>
+          <t>environ 1522</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>c.1495</t>
+          <t>environ 1495</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>c.1548</t>
+          <t>environ 1548</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>c.1600-1601</t>
+          <t>environ 1600-1601</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>c.1528</t>
+          <t>environ 1528</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>c.1536</t>
+          <t>environ 1536</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>c.1500</t>
+          <t>environ 1500</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>c.1460</t>
+          <t>environ 1460</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>c.1467</t>
+          <t>environ 1467</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>c.1530</t>
+          <t>environ 1530</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>c.1581</t>
+          <t>environ 1581</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>c.1570-1581</t>
+          <t>environ 1570-1581</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>c.1525</t>
+          <t>environ 1525</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>c.1460</t>
+          <t>environ 1460</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>environ 1487</t>
+          <t>1487 environ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>environ 1546</t>
+          <t>1546 environ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>environ 1520</t>
+          <t>1520 environ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>environ 1488</t>
+          <t>1488 environ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>environ 1470</t>
+          <t>1470 environ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1127,12 +1127,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>environ 1507</t>
+          <t>1507 environ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>environ 1568</t>
+          <t>1568 environ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>environ 1523</t>
+          <t>1523 environ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>environ 1509</t>
+          <t>1509 environ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>environ 1563</t>
+          <t>1563 environ</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>environ 1430</t>
+          <t>1430 environ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>environ 1513</t>
+          <t>1513 environ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>environ 1529</t>
+          <t>1529 environ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>environ 1485</t>
+          <t>1485 environ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>environ 1507</t>
+          <t>1507 environ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>environ 1560</t>
+          <t>1560 environ</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>environ 1495</t>
+          <t>1495 environ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>environ 1500</t>
+          <t>1500 environ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>environ 1470</t>
+          <t>1470 environ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>environ 1526</t>
+          <t>1526 environ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>environ 1500</t>
+          <t>1500 environ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>environ 1485</t>
+          <t>1485 environ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>environ 1540</t>
+          <t>1540 environ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>environ 1510</t>
+          <t>1510 environ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>environ 1565</t>
+          <t>1565 environ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>environ 1484</t>
+          <t>1484 environ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>environ 1540</t>
+          <t>1540 environ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>environ 1580</t>
+          <t>1580 environ</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>environ 1560-1570</t>
+          <t>1560-1570 environ</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>environ 1515</t>
+          <t>1515 environ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>environ 1550</t>
+          <t>1550 environ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>environ 1470</t>
+          <t>1470 environ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>environ 1530</t>
+          <t>1530 environ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>environ 1533</t>
+          <t>1533 environ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>environ 1465</t>
+          <t>1465 environ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>environ 1522</t>
+          <t>1522 environ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>environ 1495</t>
+          <t>1495 environ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>environ 1548</t>
+          <t>1548 environ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>environ 1600-1601</t>
+          <t>1600-1601 environ</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>environ 1528</t>
+          <t>1528 environ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>environ 1536</t>
+          <t>1536 environ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>environ 1500</t>
+          <t>1500 environ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>environ 1467</t>
+          <t>1467 environ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3962,17 +3962,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>environ 1530</t>
+          <t>1530 environ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>environ 1581</t>
+          <t>1581 environ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>environ 1570-1581</t>
+          <t>1570-1581 environ</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>environ 1525</t>
+          <t>1525 environ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
